--- a/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0002T0006Z000C1N46_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0002T0006Z000C1N46_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>38.20394860760304</v>
+        <v>6.208141648735494</v>
       </c>
       <c r="D2" t="n">
-        <v>39.01519624539701</v>
+        <v>6.339969389877014</v>
       </c>
       <c r="E2" t="n">
-        <v>12.17107926413221</v>
+        <v>1.977800380421484</v>
       </c>
       <c r="F2" t="n">
-        <v>11.79057731177779</v>
+        <v>1.915968813163891</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>35.34917987614917</v>
+        <v>5.744241729874241</v>
       </c>
       <c r="D3" t="n">
-        <v>37.45338570232123</v>
+        <v>6.0861751766272</v>
       </c>
       <c r="E3" t="n">
-        <v>12.17107926413221</v>
+        <v>1.977800380421484</v>
       </c>
       <c r="F3" t="n">
-        <v>11.79057731177779</v>
+        <v>1.915968813163891</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>49.04213996046567</v>
+        <v>7.969347743575671</v>
       </c>
       <c r="D4" t="n">
-        <v>48.07729384959364</v>
+        <v>7.812560250558966</v>
       </c>
       <c r="E4" t="n">
-        <v>12.17107926413221</v>
+        <v>1.977800380421484</v>
       </c>
       <c r="F4" t="n">
-        <v>11.79057731177779</v>
+        <v>1.915968813163891</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>31.88064908076413</v>
+        <v>5.180605475624171</v>
       </c>
       <c r="D5" t="n">
-        <v>30.70878478286113</v>
+        <v>4.990177527214933</v>
       </c>
       <c r="E5" t="n">
-        <v>12.17107926413221</v>
+        <v>1.977800380421484</v>
       </c>
       <c r="F5" t="n">
-        <v>11.79057731177779</v>
+        <v>1.915968813163891</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>56.48498205142447</v>
+        <v>9.178809583356475</v>
       </c>
       <c r="D6" t="n">
-        <v>54.48198053616923</v>
+        <v>8.853321837127501</v>
       </c>
       <c r="E6" t="n">
-        <v>12.17107926413221</v>
+        <v>1.977800380421484</v>
       </c>
       <c r="F6" t="n">
-        <v>11.79057731177779</v>
+        <v>1.915968813163891</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>16.04650768993834</v>
+        <v>2.60755749961498</v>
       </c>
       <c r="D7" t="n">
-        <v>15.30370245725437</v>
+        <v>2.486851649303835</v>
       </c>
       <c r="E7" t="n">
-        <v>12.17107926413221</v>
+        <v>1.977800380421484</v>
       </c>
       <c r="F7" t="n">
-        <v>11.79057731177779</v>
+        <v>1.915968813163891</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>37.06999040938954</v>
+        <v>6.023873441525801</v>
       </c>
       <c r="D8" t="n">
-        <v>37.73554734619584</v>
+        <v>6.132026443756825</v>
       </c>
       <c r="E8" t="n">
-        <v>12.17107926413221</v>
+        <v>1.977800380421484</v>
       </c>
       <c r="F8" t="n">
-        <v>11.79057731177779</v>
+        <v>1.915968813163891</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>33.48602765527011</v>
+        <v>5.441479493981394</v>
       </c>
       <c r="D9" t="n">
-        <v>31.59210932179385</v>
+        <v>5.1337177647915</v>
       </c>
       <c r="E9" t="n">
-        <v>12.17107926413221</v>
+        <v>1.977800380421484</v>
       </c>
       <c r="F9" t="n">
-        <v>11.79057731177779</v>
+        <v>1.915968813163891</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>18.01359444775179</v>
+        <v>2.927209097759666</v>
       </c>
       <c r="D10" t="n">
-        <v>19.08568533811155</v>
+        <v>3.101423867443128</v>
       </c>
       <c r="E10" t="n">
-        <v>12.17107926413221</v>
+        <v>1.977800380421484</v>
       </c>
       <c r="F10" t="n">
-        <v>11.79057731177779</v>
+        <v>1.915968813163891</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
